--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -6696,7 +6696,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -8668,7 +8668,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -6696,7 +6696,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -6696,7 +6696,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -8668,7 +8668,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -6696,7 +6696,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7374,7 +7374,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8668,7 +8668,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8820,7 +8820,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260809_202152.xlsx
@@ -5842,7 +5842,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6388,7 +6388,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
